--- a/tame_output/ON/bt/strategyON_20240127.xlsx
+++ b/tame_output/ON/bt/strategyON_20240127.xlsx
@@ -600,7 +600,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>51.3%</t>
+          <t>52.5%</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -610,7 +610,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>0.77</t>
+          <t>0.79</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -619,7 +619,7 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>1851</v>
+        <v>1852</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -628,7 +628,7 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>2024-01-25</t>
+          <t>2024-01-26</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -657,7 +657,7 @@
         </is>
       </c>
       <c r="N2" t="n">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="O2" t="inlineStr">
         <is>
@@ -681,7 +681,7 @@
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>-11.6%</t>
+          <t>-11.4%</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
@@ -746,7 +746,7 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>-4.5%</t>
+          <t>-0.2%</t>
         </is>
       </c>
     </row>
@@ -758,7 +758,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>78.1%</t>
+          <t>78.0%</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -777,7 +777,7 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>1851</v>
+        <v>1852</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -786,7 +786,7 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>2024-01-25</t>
+          <t>2024-01-26</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -849,7 +849,7 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>64.9%</t>
+          <t>64.6%</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
@@ -869,7 +869,7 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>-5.2%</t>
+          <t>-5.1%</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
@@ -904,7 +904,7 @@
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>2.3%</t>
+          <t>2.2%</t>
         </is>
       </c>
     </row>
@@ -935,7 +935,7 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>1851</v>
+        <v>1852</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -944,7 +944,7 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>2024-01-25</t>
+          <t>2024-01-26</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -1007,7 +1007,7 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>53.3%</t>
+          <t>53.5%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
@@ -1027,7 +1027,7 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>451.2%</t>
+          <t>451.5%</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
@@ -1074,7 +1074,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>101.3%</t>
+          <t>101.2%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -1084,7 +1084,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>3.26</t>
+          <t>3.25</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -1093,7 +1093,7 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>1851</v>
+        <v>1852</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -1102,7 +1102,7 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>2024-01-25</t>
+          <t>2024-01-26</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -1165,7 +1165,7 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>96.6%</t>
+          <t>96.4%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
@@ -1185,7 +1185,7 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>-18.8%</t>
+          <t>-18.7%</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>3.8%</t>
+          <t>3.6%</t>
         </is>
       </c>
     </row>
@@ -1251,7 +1251,7 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>1851</v>
+        <v>1852</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -1260,7 +1260,7 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>2024-01-25</t>
+          <t>2024-01-26</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -1323,7 +1323,7 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>66.8%</t>
+          <t>66.9%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
@@ -1348,7 +1348,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>-155.9%</t>
+          <t>-155.8%</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1390,7 +1390,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>130.5%</t>
+          <t>130.3%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -1409,7 +1409,7 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>1851</v>
+        <v>1852</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -1418,7 +1418,7 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>2024-01-25</t>
+          <t>2024-01-26</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -1481,7 +1481,7 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>124.4%</t>
+          <t>124.1%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
@@ -1501,7 +1501,7 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>-14.7%</t>
+          <t>-14.6%</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>3.9%</t>
+          <t>3.7%</t>
         </is>
       </c>
     </row>
@@ -1551,7 +1551,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G1854"/>
+  <dimension ref="A1:G1855"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -44187,7 +44187,7 @@
         <v>45316</v>
       </c>
       <c r="B1854" t="n">
-        <v>3.236238754187724</v>
+        <v>3.235981977382328</v>
       </c>
       <c r="C1854" t="n">
         <v>3.139547998939383</v>
@@ -44203,6 +44203,29 @@
       </c>
       <c r="G1854" t="n">
         <v>4.499005292306824</v>
+      </c>
+    </row>
+    <row r="1855">
+      <c r="A1855" s="2" t="n">
+        <v>45317</v>
+      </c>
+      <c r="B1855" t="n">
+        <v>3.278796973926473</v>
+      </c>
+      <c r="C1855" t="n">
+        <v>3.138090537752246</v>
+      </c>
+      <c r="D1855" t="n">
+        <v>1.651565532745382</v>
+      </c>
+      <c r="E1855" t="n">
+        <v>3.798360326536651</v>
+      </c>
+      <c r="F1855" t="n">
+        <v>2.265762155612401</v>
+      </c>
+      <c r="G1855" t="n">
+        <v>4.497547831119687</v>
       </c>
     </row>
   </sheetData>
